--- a/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_ADMIN_PW.xlsx
+++ b/reports/20260507/UI_BLOCK_UNBLOCK_FEEDBACK_ADMIN_PW.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,9 +39,13 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00991B1B"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +68,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
         <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,13 +103,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -107,6 +117,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -520,7 +533,7 @@
         </is>
       </c>
       <c r="J1" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
@@ -528,7 +541,7 @@
         </is>
       </c>
       <c r="L1" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
@@ -537,14 +550,14 @@
       </c>
       <c r="N1" s="3" t="inlineStr">
         <is>
-          <t>82.80s</t>
+          <t>73.14s</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>12:16:04</t>
+          <t>12:55:33</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -566,7 +579,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>12:16:11</t>
+          <t>12:55:45</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -588,7 +601,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>12:16:11</t>
+          <t>12:55:45</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -610,7 +623,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>12:16:11</t>
+          <t>12:55:48</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -632,7 +645,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>12:16:11</t>
+          <t>12:55:48</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -654,7 +667,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>12:16:21</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -676,7 +689,7 @@
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>12:16:21</t>
+          <t>12:55:50</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -698,7 +711,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>12:16:29</t>
+          <t>12:55:54</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -720,7 +733,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>12:16:29</t>
+          <t>12:55:55</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -742,7 +755,7 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>12:16:39</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -764,7 +777,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>12:16:39</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -786,7 +799,7 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>12:16:39</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -809,7 +822,7 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>12:16:40</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -831,7 +844,7 @@
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>12:16:40</t>
+          <t>12:56:06</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -853,7 +866,7 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>12:16:47</t>
+          <t>12:56:08</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -875,7 +888,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>12:16:47</t>
+          <t>12:56:08</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -897,7 +910,7 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>12:16:48</t>
+          <t>12:56:09</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -920,7 +933,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>12:16:48</t>
+          <t>12:56:11</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -942,7 +955,7 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>12:16:50</t>
+          <t>12:56:13</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -964,7 +977,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>12:16:51</t>
+          <t>12:56:13</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -986,7 +999,7 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>12:17:00</t>
+          <t>12:56:21</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -1008,7 +1021,7 @@
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>12:17:01</t>
+          <t>12:56:21</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -1030,7 +1043,7 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>12:17:03</t>
+          <t>12:56:23</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -1053,7 +1066,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>12:17:14</t>
+          <t>12:56:29</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1075,7 +1088,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>12:17:20</t>
+          <t>12:56:45</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1083,14 +1096,14 @@
           <t>Verify Submit Button After Unblock</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Submit Feedback button is visible after unblock</t>
+          <t>Submit Feedback button NOT visible after unblock</t>
         </is>
       </c>
     </row>
